--- a/接口测试学习/第3课_启动器登录/用例表.xlsx
+++ b/接口测试学习/第3课_启动器登录/用例表.xlsx
@@ -8,7 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="登录链路用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误码字典" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按维度分类" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类统计" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误码字典" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'登录链路用例'!$A$3:$H$39</definedName>
@@ -20,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +57,29 @@
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +131,31 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4DFEC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -135,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -183,6 +231,51 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2001,6 +2094,1998 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>《龙岛异兽：起源》启动器 · 登录链路接口测试用例表（按科学方法分类）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
+        <is>
+          <t>分类模型：测试维度（测什么）× 设计方法（怎么设计）× 优先级（先测什么）  |  共 36 条</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>用例编号</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>测试维度</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>设计方法</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>模块</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>用例标题</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>输入/步骤</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>预期结果</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>密码错误</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>your_account / wrongpwd123</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=14（密码错误）</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>密码为空</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>your_account / 空密码</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=10（密码为空）</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>账号为空</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>空账号 / your_password</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=39（账号为空）</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>账号不存在</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>nosuchuser99 / nosuchpwd</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=13（账号不存在）</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>C05</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>更新CDN</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>拉取不存在的清单</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>GET .../NoSuchGame/Manifest.json</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 404（对象不存在）</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>版本号为空</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>version=""</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=0（版本非必填校验项）</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>C06</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>更新CDN</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>拉取不存在的版本配置</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>GET .../Launcher/9.9.9.json</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 404</t>
+        </is>
+      </c>
+      <c r="H10" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>账号超长（65位）</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>a×65 / x</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=13，服务端拒绝且不崩溃</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>账号大小写敏感</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>WUYAN233 / your_password</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=13（大写不被识别）</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>账号前后含空格</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>"your_account" / your_password</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=13（未做trim）</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>账号仅1位</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>a / x</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=13</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>版本号为异常值</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>version="9.9.9"</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=0（服务端不校验）</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>错误推测</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>账号含特殊字符</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>wuyan@233 / your_password</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=13（格式校验生效）</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>正确账号密码登录</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>账号 your_account / your_password</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=0；Account=&lt;测试账号&gt;</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>B01</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>鉴权CID1401</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>用登录Token换access token</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>登录返回的 Token</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=0；返回字段2为新的 access token</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>C01</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>更新CDN</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>拉取启动器远程配置</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>GET /Preferences/Bot/Default/Launcher/0.1.json</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；返回 JSON 含 Game/Version 与 Game/Cgi/Url</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>C02</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>更新CDN</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>拉取游戏清单</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>GET /Builds/Game/Bot/0.1/Default/Raptor-Default-Test/Manifest.json</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；返回 JSON 清单</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>E01</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>拉起游戏</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>用 access token 启动游戏进程</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>以 --access-token 参数启动 Raptor-Default-Test.exe</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>游戏进程成功创建（默认关闭，见 config.json）</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>B02</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>鉴权CID1401</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>使用伪造Token（字段可解析、值无效）</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>"A"×44（带正确的 0x0A 字段标签）</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 499；code=35 ★网关在协议层直接拦截，间隔1.5s连打8次结果稳定，非限流</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>请求体缺少密码字段</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>仅发字段1=账号</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=10</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>请求体为空</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>body = 0 字节</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=39</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>B05</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>鉴权CID1401</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>请求体为空</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>body = 0 字节（完全无字段）</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=1</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>B04</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>鉴权CID1401</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Token 为空</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>字段1 = 空串（带 0x0A）</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 499；code=35（字段可解析但值为空，协议层拦截）</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>错误推测</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>缺失字段1标签(0x0A)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>按日志原文构造body（无0x0A）</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=38（参数错误）★本项目最易踩的坑</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>B03</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>错误推测</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>鉴权CID1401</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>缺字段1标签(0x0A)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>只发 长度+Token（解析不出字段1）</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=1 ★与B02对照：字段能否解析决定走协议层还是业务层</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>B06</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>会话与状态</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>状态迁移</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>鉴权CID1401</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>单会话互踢：新登录顶掉旧Token</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>登录取T1 → 跨秒后再登录 → 用T1换access token</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>旧T1 被拒：HTTP 499；code=35 ★说明启动器拉起游戏前必须重换token</t>
+        </is>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>B07</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>会话与状态</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>状态迁移</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>鉴权CID1401</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>重新登录后Token立即恢复可用</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>用最新一次登录的Token换access token</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=0；返回新 access token</t>
+        </is>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>会话与状态</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>状态迁移</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>重复登录</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>同参数连续登录 2 次</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>两次均 code=0，服务端不报"重复登录"</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>数据完整性</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>登录返回昵称与Token</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>同 A01</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>Name 字段非空；Token 为 44 位字符串</t>
+        </is>
+      </c>
+      <c r="H32" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>C04</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>数据完整性</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>更新CDN</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>本地版本与远程版本一致</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>本地 game=0.1 / 远程 Game/Version=0.1</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>判定"无需更新"</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>数据完整性</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>昵称与账号不一致</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>nickname="测试昵称"</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 200；code=0，返回昵称以账号数据为准</t>
+        </is>
+      </c>
+      <c r="H34" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>数据完整性</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>登录CID1396</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>HTTP状态码恒为200</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>上述所有错误输入</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 状态码全部为 200，成败只体现在响应体 code ★</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>数据完整性</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>更新CDN</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>清单MD5完整性校验</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>下载 Manifest.json 并计算 MD5，与同名 .md5 比对</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>实际 MD5 == 声明 MD5</t>
+        </is>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>D01</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>网关健壮性</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>网关健壮性</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>缺少 CID 路由头</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>POST 网关，不带头 CID</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 500；响应体 "no route for cid -1"</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>D02</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>网关健壮性</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>网关健壮性</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>使用不存在的 CID</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>CID = 9999</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 500；响应体 "no route for cid 9999"</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>D03</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>网关健壮性</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>网关健壮性</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>使用 GET 方法</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>GET 网关</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 501；响应体 "invalid method GET"</t>
+        </is>
+      </c>
+      <c r="H39" s="22" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>分类统计矩阵：测试维度 × 设计方法</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>测试维度 \ 设计方法</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>等价类划分</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>边界值分析</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>错误推测</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>状态迁移</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>场景法</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="25" t="inlineStr">
+        <is>
+          <t>功能正确性</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>协议健壮性</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>会话与状态</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>数据完整性</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>网关健壮性</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr"/>
+      <c r="D8" s="4" t="inlineStr"/>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B9" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="C9" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>分类依据说明：</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>1. 测试维度 —— 该用例验证的系统性质。一条用例只归属一个维度，避免以往「正常/异常」与「边界值」等不同层次混列的问题。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>2. 设计方法 —— 该用例由哪种用例设计技术推导得出，用于评估覆盖质量（等价类是否全覆盖、边界是否取到）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>3. 优先级    —— 按业务影响与失败概率排序，指导执行顺序与冒烟范围。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="30" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>测试维度分布：</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>· 功能正确性        18 条（50.0%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>· 协议健壮性         7 条（19.4%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>· 会话与状态         3 条（ 8.3%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>· 数据完整性         5 条（13.9%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="30" t="inlineStr">
+        <is>
+          <t>· 网关健壮性         3 条（ 8.3%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="30" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>设计方法分布：</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>· 等价类划分        17 条（47.2%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>· 边界值分析         6 条（16.7%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>· 错误推测          3 条（ 8.3%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>· 状态迁移          3 条（ 8.3%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>· 场景法           7 条（19.4%）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="31" t="inlineStr">
+        <is>
+          <t>覆盖度自检：</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>· 等价类划分同时覆盖有效类（A01/B01/C01 等）与无效类（A03-A06 凭据类、A12/A13/B05 字段缺失类、</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D01-D03 路由与协议类、C05/C06 资源不存在类），等价类划分完整。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>· 边界值分析覆盖长度边界（A07 超长 / A08 仅1位）、字符集边界（A10 大小写）、</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  输入边界（A11 前后空格）、取值边界（A16 版本异常值 / B04 空 token），边界取值完整。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>· 状态迁移集中在「会话与状态」维度（A18 重复登录 / B06 单会话互踢 / B07 重登恢复），</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  三条用例共同刻画网关 token 按秒派生、新登录顶掉旧 token 的状态机。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>· 错误推测仅保留 2 条（A09 特殊字符 / A14、B03 缺 0x0A 标签），前者凭经验、</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  后者源自私有协议逆向发现，确实无法通过等价类或边界值推导。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="30" t="inlineStr">
+        <is>
+          <t>结论：覆盖以等价类划分为主（33.3%），边界值与场景法辅助，错误推测占比降至 8.3%，</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="inlineStr">
+        <is>
+          <t>说明用例集的主体是可推导的、可评审的，而非依赖个人经验，覆盖质量可控。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
